--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104580_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104580_W14.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6028</v>
+        <v>3.5161</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8547</v>
+        <v>6.6109</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.2519</v>
+        <v>-3.0947</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1703</v>
+        <v>0.1504</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0651</v>
+        <v>3.0509</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.8948</v>
+        <v>-2.9005</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8685</v>
+        <v>3.8169</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9167</v>
+        <v>3.8848</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0481</v>
+        <v>-0.0679</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.6983</v>
+        <v>-3.6665</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.8467</v>
+        <v>-2.8326</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5402</v>
+        <v>-0.5157</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6816</v>
+        <v>0.506</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1414</v>
+        <v>-1.0217</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4164</v>
+        <v>1.2023</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0885</v>
+        <v>3.9408</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.6721</v>
+        <v>-2.7386</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4557</v>
+        <v>0.4474</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3967</v>
+        <v>1.4013</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.9539</v>
       </c>
       <c r="J3" t="n">
-        <v>3.155</v>
+        <v>3.1246</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5239</v>
+        <v>1.5168</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6311</v>
+        <v>1.6077</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6993</v>
+        <v>-2.6772</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.5721</v>
+        <v>-2.5617</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0808</v>
+        <v>-0.2938</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3871</v>
+        <v>0.2715</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4679</v>
+        <v>-0.5653</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3691</v>
+        <v>-0.6614</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6038</v>
+        <v>1.2274</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9729</v>
+        <v>-1.8888</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6455</v>
+        <v>0.6418</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4344</v>
+        <v>1.4251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7889</v>
+        <v>-0.7833</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8094</v>
+        <v>1.7874</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7348</v>
+        <v>1.713</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1639</v>
+        <v>-1.1457</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3756</v>
+        <v>-0.669</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0212</v>
+        <v>-0.3324</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3968</v>
+        <v>-0.3366</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8023</v>
+        <v>-0.8037</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2165</v>
+        <v>-0.1984</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5858</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4282</v>
+        <v>-1.2695</v>
       </c>
       <c r="H5" t="n">
-        <v>1.531</v>
+        <v>-0.8213</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.9592</v>
+        <v>-0.4482</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5784</v>
+        <v>-0.3527</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5168</v>
+        <v>-0.3899</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.9383</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0066</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0142</v>
+        <v>-0.4314</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0209</v>
+        <v>-0.4854</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5329</v>
+        <v>-0.5342</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1785</v>
+        <v>-0.3904</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7114</v>
+        <v>-0.1438</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3856</v>
+        <v>0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9157</v>
+        <v>-0.881</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4203</v>
+        <v>0.9296</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4954</v>
+        <v>-1.8106</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2727</v>
+        <v>1.2272</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8196</v>
+        <v>0.5595</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4531</v>
+        <v>0.6676</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3405</v>
+        <v>2.0277</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3779</v>
+        <v>0.7617</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>1.2661</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9321</v>
+        <v>-0.8006</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4417</v>
+        <v>-0.2022</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4904</v>
+        <v>-0.5984</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.643</v>
+        <v>-1.5422</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6261</v>
+        <v>-0.4835</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0169</v>
+        <v>-1.0587</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>-1.4764</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5463</v>
+        <v>-0.387</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2433</v>
+        <v>-1.0987</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4728</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.716</v>
+        <v>-0.5004</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2107</v>
+        <v>-0.4311</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5496</v>
+        <v>1.5308</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6611</v>
+        <v>-1.9619</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0409</v>
+        <v>0.5566</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7721</v>
+        <v>1.5029</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2688</v>
+        <v>-0.9463</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8302</v>
+        <v>-0.9877</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2225</v>
+        <v>0.028</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6077</v>
+        <v>-1.0157</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.883</v>
+        <v>-0.8269</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9557</v>
+        <v>-0.1745</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9273</v>
+        <v>-0.6524</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4783</v>
+        <v>0.387</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.53</v>
+        <v>-1.5716</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0846</v>
+        <v>3.0672</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.6146</v>
+        <v>-4.6388</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9208</v>
+        <v>-0.901</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7473</v>
+        <v>1.7544</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6681</v>
+        <v>-2.6554</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9507</v>
+        <v>2.9379</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6148</v>
+        <v>2.6028</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3359</v>
+        <v>0.3351</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.8715</v>
+        <v>-3.8389</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8675</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.0039</v>
+        <v>-2.9906</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.9454</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0393</v>
+        <v>0.0414</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9188</v>
+        <v>-0.9868</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1228</v>
+        <v>-1.5755</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3783</v>
+        <v>2.9215</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.5011</v>
+        <v>-4.4971</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0635</v>
+        <v>1.0585</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2265</v>
+        <v>-0.2269</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2901</v>
+        <v>1.2853</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5459</v>
+        <v>4.5105</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7824</v>
+        <v>0.7649</v>
       </c>
       <c r="L9" t="n">
-        <v>3.7636</v>
+        <v>3.7456</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4824</v>
+        <v>-3.4521</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0089</v>
+        <v>-0.9918</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4735</v>
+        <v>-2.4603</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5059</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7652</v>
+        <v>-0.1745</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7407</v>
+        <v>-0.7766</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0567</v>
+        <v>-2.4112</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0745</v>
+        <v>1.5365</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.1312</v>
+        <v>-3.9477</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9292</v>
+        <v>-1.9175</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0736</v>
+        <v>-1.0687</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8556</v>
+        <v>-0.8488</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5614</v>
+        <v>1.5506</v>
       </c>
       <c r="K10" t="n">
-        <v>0.218</v>
+        <v>0.2101</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.4906</v>
+        <v>-3.4681</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.199</v>
+        <v>-2.1893</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1689</v>
+        <v>-0.5424</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4869</v>
+        <v>-0.0141</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.5283</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3364</v>
+        <v>-4.0842</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2927</v>
+        <v>-1.0957</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0437</v>
+        <v>-2.9885</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9948</v>
+        <v>-3.0061</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5683</v>
+        <v>-2.5786</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4265</v>
+        <v>-0.4276</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9382</v>
+        <v>-0.971</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9057</v>
+        <v>-1.9315</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0566</v>
+        <v>-2.0351</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4097</v>
+        <v>-1.1463</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8347</v>
+        <v>-0.5995</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.575</v>
+        <v>-0.5468</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.357099999999999</v>
+        <v>-8.3689</v>
       </c>
       <c r="E12" t="n">
-        <v>18.6277</v>
+        <v>18.3415</v>
       </c>
       <c r="F12" t="n">
-        <v>-26.9847</v>
+        <v>-26.7105</v>
       </c>
       <c r="G12" t="n">
-        <v>-4</v>
+        <v>-3.9999</v>
       </c>
       <c r="H12" t="n">
-        <v>5.036100000000001</v>
+        <v>5.0265</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.036000000000001</v>
+        <v>-9.026700000000002</v>
       </c>
       <c r="J12" t="n">
-        <v>19.2315</v>
+        <v>18.9885</v>
       </c>
       <c r="K12" t="n">
-        <v>10.7959</v>
+        <v>10.6356</v>
       </c>
       <c r="L12" t="n">
-        <v>8.435799999999999</v>
+        <v>8.353</v>
       </c>
       <c r="M12" t="n">
-        <v>-23.2315</v>
+        <v>-22.9887</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.7598</v>
+        <v>-5.6089</v>
       </c>
       <c r="O12" t="n">
-        <v>-17.47179999999999</v>
+        <v>-17.3799</v>
       </c>
       <c r="P12" t="n">
-        <v>5.6709</v>
+        <v>5.6909</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.670800000000001</v>
+        <v>-5.6907</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.9391</v>
+        <v>-7.967</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3609</v>
+        <v>-1.35</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.578200000000001</v>
+        <v>-6.617</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.0889</v>
+        <v>-2.0926</v>
       </c>
       <c r="W12" t="n">
-        <v>6.427599999999999</v>
+        <v>6.393899999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.5166</v>
+        <v>-8.486700000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5269</v>
+        <v>7.6548</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7793</v>
+        <v>7.5993</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2524</v>
+        <v>0.0555</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3517</v>
+        <v>2.5152</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2135</v>
+        <v>1.8872</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1382</v>
+        <v>0.628</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6855</v>
+        <v>3.2593</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7824</v>
+        <v>2.2473</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9032</v>
+        <v>1.012</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3338</v>
+        <v>-0.7441</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5689</v>
+        <v>-0.3601</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7649</v>
+        <v>-0.384</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6288</v>
+        <v>1.2566</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9084</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7204</v>
+        <v>0.5021</v>
       </c>
       <c r="V13" t="n">
-        <v>1.639</v>
+        <v>3.6554</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1853</v>
+        <v>3.8132</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0822</v>
+        <v>5.8891</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5916</v>
+        <v>6.1688</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5095</v>
+        <v>-0.2797</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5341</v>
+        <v>1.3608</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8918</v>
+        <v>0.218</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6423</v>
+        <v>1.1427</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3056</v>
+        <v>2.664</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2716</v>
+        <v>0.7649</v>
       </c>
       <c r="L14" t="n">
-        <v>1.034</v>
+        <v>1.8991</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7716</v>
+        <v>-1.3032</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3798</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3918</v>
+        <v>-0.7563</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3424</v>
+        <v>1.9836</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3115</v>
+        <v>1.3258</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0309</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>3.6636</v>
+        <v>1.6342</v>
       </c>
       <c r="W14" t="n">
-        <v>3.8243</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1594</v>
+        <v>3.8534</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2376</v>
+        <v>7.0232</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.0783</v>
+        <v>-3.1698</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4314</v>
+        <v>5.4271</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4242</v>
+        <v>-1.4218</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8557</v>
+        <v>6.849</v>
       </c>
       <c r="J15" t="n">
-        <v>8.9747</v>
+        <v>8.9398</v>
       </c>
       <c r="K15" t="n">
-        <v>0.765</v>
+        <v>0.7477</v>
       </c>
       <c r="L15" t="n">
-        <v>8.2097</v>
+        <v>8.1921</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.5433</v>
+        <v>-3.5127</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.1893</v>
+        <v>-2.1695</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.7921</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2419</v>
+        <v>0.5874</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3309</v>
+        <v>0.2047</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7076</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3707</v>
+        <v>1.9374</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6631</v>
+        <v>-1.0327</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6556</v>
+        <v>-0.6481</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6984</v>
+        <v>-0.7007</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0427</v>
+        <v>0.0526</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8514</v>
+        <v>0.8275</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5155</v>
+        <v>0.4924</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3359</v>
+        <v>0.3351</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.507</v>
+        <v>-1.4756</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2139</v>
+        <v>-1.1931</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7754</v>
+        <v>1.9594</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7462</v>
+        <v>1.3375</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0292</v>
+        <v>0.6218</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3255</v>
+        <v>0.5461</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9715</v>
+        <v>4.1381</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.646</v>
+        <v>-3.5921</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0204</v>
+        <v>0.0118</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8139</v>
+        <v>-1.6832</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8343</v>
+        <v>1.6949</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5995</v>
+        <v>3.7376</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4129</v>
+        <v>-0.0452</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1866</v>
+        <v>3.7828</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6198</v>
+        <v>-3.7258</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.599</v>
+        <v>-1.638</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0209</v>
+        <v>-2.0879</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.4952</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3874</v>
+        <v>0.1277</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8672</v>
+        <v>0.3597</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5202</v>
+        <v>-0.232</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5538</v>
+        <v>-0.7413</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3518</v>
+        <v>-1.0614</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.9056</v>
+        <v>0.3201</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0152</v>
+        <v>1.3202</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6854</v>
+        <v>-0.3452</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7006</v>
+        <v>1.6654</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7694</v>
+        <v>1.2778</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0315</v>
+        <v>0.0862</v>
       </c>
       <c r="L18" t="n">
-        <v>3.8009</v>
+        <v>1.1916</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.7542</v>
+        <v>0.0424</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6539</v>
+        <v>-0.4314</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1003</v>
+        <v>0.4738</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5878</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9811</v>
+        <v>-0.0128</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4688</v>
+        <v>-0.0629</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5123</v>
+        <v>0.0501</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0188</v>
+        <v>-0.9627</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6927</v>
+        <v>2.4436</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.7115</v>
+        <v>-3.4064</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5938</v>
+        <v>-0.5866</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.863</v>
+        <v>-0.8562</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2692</v>
+        <v>0.2696</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0919</v>
+        <v>2.0802</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1914</v>
+        <v>1.1839</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6857</v>
+        <v>-2.6668</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7635</v>
+        <v>-1.7526</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0375</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5081</v>
+        <v>0.2739</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5456</v>
+        <v>-0.2647</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3165</v>
+        <v>-1.6001</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.405</v>
+        <v>0.1847</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0885</v>
+        <v>-1.7849</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3108</v>
+        <v>-0.0194</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3551</v>
+        <v>0.8101</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6659</v>
+        <v>-0.8295</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2807</v>
+        <v>1.5856</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0866</v>
+        <v>1.3994</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1941</v>
+        <v>0.1862</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0301</v>
+        <v>-1.605</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4417</v>
+        <v>-0.5893</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4718</v>
+        <v>-1.0157</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0415</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5858</v>
+        <v>1.4679</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4174</v>
+        <v>1.1031</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1685</v>
+        <v>0.3648</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9901</v>
+        <v>-2.6018</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5157</v>
+        <v>1.0851</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5058</v>
+        <v>-3.6869</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7894</v>
+        <v>-1.7859</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0563</v>
+        <v>-1.0514</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.733</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1599</v>
+        <v>1.1387</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7548</v>
+        <v>0.7444</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4051</v>
+        <v>0.3943</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9493</v>
+        <v>-2.9246</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8112</v>
+        <v>-1.7959</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3064</v>
+        <v>0.064</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4174</v>
+        <v>0.174</v>
       </c>
       <c r="U21" t="n">
-        <v>0.111</v>
+        <v>-0.11</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5748</v>
+        <v>-1.5628</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5748</v>
+        <v>-1.5628</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5652</v>
+        <v>-3.7835</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1213</v>
+        <v>-2.8084</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4439</v>
+        <v>-0.9751</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5841</v>
+        <v>-3.5951</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8728</v>
+        <v>-1.8835</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7113</v>
+        <v>-1.7116</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.487</v>
+        <v>-2.522</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.6979</v>
+        <v>-1.7247</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7891</v>
+        <v>-0.7973</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0971</v>
+        <v>-1.0731</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3118</v>
+        <v>1.109</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4053</v>
+        <v>0.7638</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0935</v>
+        <v>0.3452</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8.357200000000002</v>
+        <v>9.1587</v>
       </c>
       <c r="E23" t="n">
-        <v>26.9846</v>
+        <v>26.7104</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.6276</v>
+        <v>-17.552</v>
       </c>
       <c r="G23" t="n">
-        <v>3.9999</v>
+        <v>4.000000000000002</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.036</v>
+        <v>-5.0267</v>
       </c>
       <c r="I23" t="n">
-        <v>9.035999999999998</v>
+        <v>9.026699999999998</v>
       </c>
       <c r="J23" t="n">
-        <v>23.2316</v>
+        <v>22.9885</v>
       </c>
       <c r="K23" t="n">
-        <v>5.759900000000001</v>
+        <v>5.608700000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>17.4718</v>
+        <v>17.3798</v>
       </c>
       <c r="M23" t="n">
-        <v>-19.2317</v>
+        <v>-18.9885</v>
       </c>
       <c r="N23" t="n">
-        <v>-10.7961</v>
+        <v>-10.6356</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.435699999999999</v>
+        <v>-8.353200000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.6709</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-11.3416</v>
+        <v>-11.3814</v>
       </c>
       <c r="R23" t="n">
-        <v>5.6707</v>
+        <v>5.6907</v>
       </c>
       <c r="S23" t="n">
-        <v>7.9391</v>
+        <v>8.7568</v>
       </c>
       <c r="T23" t="n">
-        <v>6.578200000000001</v>
+        <v>6.6168</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3609</v>
+        <v>2.1398</v>
       </c>
       <c r="V23" t="n">
-        <v>2.0889</v>
+        <v>2.0926</v>
       </c>
       <c r="W23" t="n">
-        <v>8.516300000000001</v>
+        <v>8.486500000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.427599999999999</v>
+        <v>-6.393899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104580_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104580_W14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-8.486700000000001</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104580_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-6.393899999999999</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
